--- a/Data/EXCEL/Transfer/salemon/202208/6617-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/6617-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F9161FB-A9F9-471E-A77A-90FCD87468BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{58862E34-EB8F-4666-8FA3-BC7F6CC0CDE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="6617-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1218,19 +1226,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:Q72"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.625" customWidth="1"/>
-    <col min="2" max="5" width="9.75" customWidth="1"/>
-    <col min="6" max="7" width="10.625" customWidth="1"/>
-    <col min="8" max="8" width="11.125" customWidth="1"/>
-    <col min="9" max="10" width="9.25" customWidth="1"/>
-    <col min="11" max="11" width="11.125" customWidth="1"/>
-    <col min="12" max="12" width="9.75" customWidth="1"/>
-    <col min="13" max="13" width="11.125" customWidth="1"/>
-    <col min="14" max="15" width="9.25" customWidth="1"/>
-    <col min="16" max="17" width="11.125" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="5" width="13.75" customWidth="1"/>
+    <col min="6" max="7" width="15.125" customWidth="1"/>
+    <col min="8" max="8" width="15.75" customWidth="1"/>
+    <col min="9" max="10" width="13.125" customWidth="1"/>
+    <col min="11" max="11" width="15.75" customWidth="1"/>
+    <col min="12" max="12" width="13.75" customWidth="1"/>
+    <col min="13" max="13" width="15.75" customWidth="1"/>
+    <col min="14" max="15" width="13.125" customWidth="1"/>
+    <col min="16" max="16" width="15.75" customWidth="1"/>
+    <col min="17" max="17" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1383,25 +1392,25 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B5" s="7">
-        <v>289.5</v>
+        <v>396</v>
       </c>
       <c r="C5" s="7">
-        <v>396</v>
+        <v>424.5</v>
       </c>
       <c r="D5" s="7">
-        <v>407.5</v>
+        <v>457</v>
       </c>
       <c r="E5" s="7">
-        <v>273.5</v>
+        <v>368</v>
       </c>
       <c r="F5" s="8">
-        <v>106.5</v>
+        <v>28.5</v>
       </c>
       <c r="G5" s="8">
-        <v>36.79</v>
+        <v>7.2</v>
       </c>
       <c r="H5" s="9">
         <v>0</v>
@@ -1436,25 +1445,25 @@
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B6" s="7">
-        <v>258</v>
+        <v>289.5</v>
       </c>
       <c r="C6" s="7">
-        <v>289.5</v>
+        <v>396</v>
       </c>
       <c r="D6" s="7">
-        <v>292.5</v>
+        <v>407.5</v>
       </c>
       <c r="E6" s="7">
-        <v>247.5</v>
+        <v>273.5</v>
       </c>
       <c r="F6" s="8">
-        <v>31.5</v>
+        <v>106.5</v>
       </c>
       <c r="G6" s="8">
-        <v>12.21</v>
+        <v>36.79</v>
       </c>
       <c r="H6" s="9">
         <v>0</v>
@@ -1489,25 +1498,25 @@
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B7" s="7">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C7" s="7">
-        <v>258</v>
+        <v>289.5</v>
       </c>
       <c r="D7" s="7">
-        <v>276</v>
+        <v>292.5</v>
       </c>
       <c r="E7" s="7">
-        <v>240.5</v>
-      </c>
-      <c r="F7" s="10">
-        <v>-6</v>
-      </c>
-      <c r="G7" s="10">
-        <v>-2.27</v>
+        <v>247.5</v>
+      </c>
+      <c r="F7" s="8">
+        <v>31.5</v>
+      </c>
+      <c r="G7" s="8">
+        <v>12.21</v>
       </c>
       <c r="H7" s="9">
         <v>0</v>
@@ -1542,25 +1551,25 @@
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B8" s="7">
-        <v>249.5</v>
+        <v>264</v>
       </c>
       <c r="C8" s="7">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D8" s="7">
-        <v>265.5</v>
+        <v>276</v>
       </c>
       <c r="E8" s="7">
-        <v>242.5</v>
-      </c>
-      <c r="F8" s="8">
-        <v>14.5</v>
-      </c>
-      <c r="G8" s="8">
-        <v>5.81</v>
+        <v>240.5</v>
+      </c>
+      <c r="F8" s="10">
+        <v>-6</v>
+      </c>
+      <c r="G8" s="10">
+        <v>-2.27</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -1595,25 +1604,25 @@
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B9" s="7">
-        <v>268.5</v>
+        <v>249.5</v>
       </c>
       <c r="C9" s="7">
-        <v>249.5</v>
+        <v>264</v>
       </c>
       <c r="D9" s="7">
-        <v>268.5</v>
+        <v>265.5</v>
       </c>
       <c r="E9" s="7">
-        <v>229.5</v>
-      </c>
-      <c r="F9" s="10">
-        <v>-19</v>
-      </c>
-      <c r="G9" s="10">
-        <v>-7.08</v>
+        <v>242.5</v>
+      </c>
+      <c r="F9" s="8">
+        <v>14.5</v>
+      </c>
+      <c r="G9" s="8">
+        <v>5.81</v>
       </c>
       <c r="H9" s="9">
         <v>0</v>
@@ -1648,25 +1657,25 @@
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B10" s="7">
+        <v>268.5</v>
+      </c>
+      <c r="C10" s="7">
         <v>249.5</v>
       </c>
-      <c r="C10" s="7">
+      <c r="D10" s="7">
         <v>268.5</v>
       </c>
-      <c r="D10" s="7">
-        <v>309.5</v>
-      </c>
       <c r="E10" s="7">
-        <v>249.5</v>
-      </c>
-      <c r="F10" s="8">
-        <v>19</v>
-      </c>
-      <c r="G10" s="8">
-        <v>7.62</v>
+        <v>229.5</v>
+      </c>
+      <c r="F10" s="10">
+        <v>-19</v>
+      </c>
+      <c r="G10" s="10">
+        <v>-7.08</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -1701,25 +1710,25 @@
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B11" s="7">
-        <v>283</v>
+        <v>249.5</v>
       </c>
       <c r="C11" s="7">
+        <v>268.5</v>
+      </c>
+      <c r="D11" s="7">
+        <v>309.5</v>
+      </c>
+      <c r="E11" s="7">
         <v>249.5</v>
       </c>
-      <c r="D11" s="7">
-        <v>304.5</v>
-      </c>
-      <c r="E11" s="7">
-        <v>225</v>
-      </c>
-      <c r="F11" s="10">
-        <v>-33.5</v>
-      </c>
-      <c r="G11" s="10">
-        <v>-11.84</v>
+      <c r="F11" s="8">
+        <v>19</v>
+      </c>
+      <c r="G11" s="8">
+        <v>7.62</v>
       </c>
       <c r="H11" s="9">
         <v>0</v>
@@ -1754,134 +1763,134 @@
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B12" s="7">
-        <v>239.5</v>
+        <v>283</v>
       </c>
       <c r="C12" s="7">
-        <v>283</v>
+        <v>249.5</v>
       </c>
       <c r="D12" s="7">
-        <v>310</v>
+        <v>304.5</v>
       </c>
       <c r="E12" s="7">
-        <v>231.5</v>
-      </c>
-      <c r="F12" s="8">
-        <v>43.5</v>
-      </c>
-      <c r="G12" s="8">
-        <v>18.16</v>
+        <v>225</v>
+      </c>
+      <c r="F12" s="10">
+        <v>-33.5</v>
+      </c>
+      <c r="G12" s="10">
+        <v>-11.84</v>
       </c>
       <c r="H12" s="9">
         <v>0</v>
       </c>
-      <c r="I12" s="10">
-        <v>-100</v>
-      </c>
-      <c r="J12" s="10">
-        <v>-100</v>
+      <c r="I12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K12" s="9">
-        <v>1.14E-2</v>
-      </c>
-      <c r="L12" s="8">
-        <v>37.200000000000003</v>
+        <v>0</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M12" s="9">
         <v>0</v>
       </c>
-      <c r="N12" s="10">
-        <v>-100</v>
-      </c>
-      <c r="O12" s="10">
-        <v>-100</v>
+      <c r="N12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P12" s="9">
-        <v>1.14E-2</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>37.200000000000003</v>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B13" s="7">
-        <v>214.5</v>
+        <v>239.5</v>
       </c>
       <c r="C13" s="7">
-        <v>239.5</v>
+        <v>283</v>
       </c>
       <c r="D13" s="7">
-        <v>239.5</v>
+        <v>310</v>
       </c>
       <c r="E13" s="7">
-        <v>196</v>
+        <v>231.5</v>
       </c>
       <c r="F13" s="8">
-        <v>25</v>
+        <v>43.5</v>
       </c>
       <c r="G13" s="8">
-        <v>11.66</v>
+        <v>18.16</v>
       </c>
       <c r="H13" s="9">
-        <v>1.14E-2</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I13" s="10">
+        <v>-100</v>
+      </c>
+      <c r="J13" s="10">
+        <v>-100</v>
       </c>
       <c r="K13" s="9">
         <v>1.14E-2</v>
       </c>
-      <c r="L13" s="9" t="s">
-        <v>17</v>
+      <c r="L13" s="8">
+        <v>37.200000000000003</v>
       </c>
       <c r="M13" s="9">
-        <v>1.14E-2</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N13" s="10">
+        <v>-100</v>
+      </c>
+      <c r="O13" s="10">
+        <v>-100</v>
       </c>
       <c r="P13" s="9">
         <v>1.14E-2</v>
       </c>
-      <c r="Q13" s="9" t="s">
-        <v>17</v>
+      <c r="Q13" s="8">
+        <v>37.200000000000003</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B14" s="7">
-        <v>234.5</v>
+        <v>214.5</v>
       </c>
       <c r="C14" s="7">
-        <v>214.5</v>
+        <v>239.5</v>
       </c>
       <c r="D14" s="7">
-        <v>234.5</v>
+        <v>239.5</v>
       </c>
       <c r="E14" s="7">
-        <v>189</v>
-      </c>
-      <c r="F14" s="10">
-        <v>-20</v>
-      </c>
-      <c r="G14" s="10">
-        <v>-8.5299999999999994</v>
+        <v>196</v>
+      </c>
+      <c r="F14" s="8">
+        <v>25</v>
+      </c>
+      <c r="G14" s="8">
+        <v>11.66</v>
       </c>
       <c r="H14" s="9">
-        <v>0</v>
+        <v>1.14E-2</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>17</v>
@@ -1890,13 +1899,13 @@
         <v>17</v>
       </c>
       <c r="K14" s="9">
-        <v>0</v>
+        <v>1.14E-2</v>
       </c>
       <c r="L14" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M14" s="9">
-        <v>0</v>
+        <v>1.14E-2</v>
       </c>
       <c r="N14" s="9" t="s">
         <v>17</v>
@@ -1905,7 +1914,7 @@
         <v>17</v>
       </c>
       <c r="P14" s="9">
-        <v>0</v>
+        <v>1.14E-2</v>
       </c>
       <c r="Q14" s="9" t="s">
         <v>17</v>
@@ -1913,25 +1922,25 @@
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B15" s="7">
-        <v>215.5</v>
+        <v>234.5</v>
       </c>
       <c r="C15" s="7">
+        <v>214.5</v>
+      </c>
+      <c r="D15" s="7">
         <v>234.5</v>
       </c>
-      <c r="D15" s="7">
-        <v>239.5</v>
-      </c>
       <c r="E15" s="7">
-        <v>208</v>
-      </c>
-      <c r="F15" s="8">
-        <v>19</v>
-      </c>
-      <c r="G15" s="8">
-        <v>8.82</v>
+        <v>189</v>
+      </c>
+      <c r="F15" s="10">
+        <v>-20</v>
+      </c>
+      <c r="G15" s="10">
+        <v>-8.5299999999999994</v>
       </c>
       <c r="H15" s="9">
         <v>0</v>
@@ -1966,25 +1975,25 @@
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B16" s="7">
-        <v>209.5</v>
+        <v>215.5</v>
       </c>
       <c r="C16" s="7">
-        <v>215.5</v>
+        <v>234.5</v>
       </c>
       <c r="D16" s="7">
-        <v>229.5</v>
+        <v>239.5</v>
       </c>
       <c r="E16" s="7">
-        <v>200.5</v>
+        <v>208</v>
       </c>
       <c r="F16" s="8">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G16" s="8">
-        <v>2.86</v>
+        <v>8.82</v>
       </c>
       <c r="H16" s="9">
         <v>0</v>
@@ -2019,25 +2028,25 @@
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B17" s="7">
+        <v>209.5</v>
+      </c>
+      <c r="C17" s="7">
+        <v>215.5</v>
+      </c>
+      <c r="D17" s="7">
         <v>229.5</v>
       </c>
-      <c r="C17" s="7">
-        <v>209.5</v>
-      </c>
-      <c r="D17" s="7">
-        <v>263.5</v>
-      </c>
       <c r="E17" s="7">
-        <v>200</v>
-      </c>
-      <c r="F17" s="10">
-        <v>-20</v>
-      </c>
-      <c r="G17" s="10">
-        <v>-8.7100000000000009</v>
+        <v>200.5</v>
+      </c>
+      <c r="F17" s="8">
+        <v>6</v>
+      </c>
+      <c r="G17" s="8">
+        <v>2.86</v>
       </c>
       <c r="H17" s="9">
         <v>0</v>
@@ -2072,25 +2081,25 @@
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B18" s="7">
-        <v>193</v>
+        <v>229.5</v>
       </c>
       <c r="C18" s="7">
-        <v>229.5</v>
+        <v>209.5</v>
       </c>
       <c r="D18" s="7">
-        <v>231</v>
+        <v>263.5</v>
       </c>
       <c r="E18" s="7">
-        <v>179</v>
-      </c>
-      <c r="F18" s="8">
-        <v>36.5</v>
-      </c>
-      <c r="G18" s="8">
-        <v>18.91</v>
+        <v>200</v>
+      </c>
+      <c r="F18" s="10">
+        <v>-20</v>
+      </c>
+      <c r="G18" s="10">
+        <v>-8.7100000000000009</v>
       </c>
       <c r="H18" s="9">
         <v>0</v>
@@ -2125,25 +2134,25 @@
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B19" s="7">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="C19" s="7">
-        <v>193</v>
+        <v>229.5</v>
       </c>
       <c r="D19" s="7">
-        <v>202.5</v>
+        <v>231</v>
       </c>
       <c r="E19" s="7">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="F19" s="8">
-        <v>15</v>
+        <v>36.5</v>
       </c>
       <c r="G19" s="8">
-        <v>8.43</v>
+        <v>18.91</v>
       </c>
       <c r="H19" s="9">
         <v>0</v>
@@ -2178,25 +2187,25 @@
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B20" s="7">
-        <v>190.5</v>
+        <v>178</v>
       </c>
       <c r="C20" s="7">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="D20" s="7">
-        <v>225</v>
+        <v>202.5</v>
       </c>
       <c r="E20" s="7">
-        <v>175.5</v>
-      </c>
-      <c r="F20" s="10">
-        <v>-12.5</v>
-      </c>
-      <c r="G20" s="10">
-        <v>-6.56</v>
+        <v>150</v>
+      </c>
+      <c r="F20" s="8">
+        <v>15</v>
+      </c>
+      <c r="G20" s="8">
+        <v>8.43</v>
       </c>
       <c r="H20" s="9">
         <v>0</v>
@@ -2231,25 +2240,25 @@
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B21" s="7">
-        <v>208.5</v>
+        <v>190.5</v>
       </c>
       <c r="C21" s="7">
-        <v>190.5</v>
+        <v>178</v>
       </c>
       <c r="D21" s="7">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="E21" s="7">
-        <v>175</v>
+        <v>175.5</v>
       </c>
       <c r="F21" s="10">
-        <v>-18</v>
+        <v>-12.5</v>
       </c>
       <c r="G21" s="10">
-        <v>-8.6300000000000008</v>
+        <v>-6.56</v>
       </c>
       <c r="H21" s="9">
         <v>0</v>
@@ -2284,25 +2293,25 @@
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B22" s="7">
-        <v>188.5</v>
+        <v>208.5</v>
       </c>
       <c r="C22" s="7">
-        <v>208.5</v>
+        <v>190.5</v>
       </c>
       <c r="D22" s="7">
-        <v>211.5</v>
+        <v>211</v>
       </c>
       <c r="E22" s="7">
-        <v>140</v>
-      </c>
-      <c r="F22" s="8">
-        <v>20</v>
-      </c>
-      <c r="G22" s="8">
-        <v>10.61</v>
+        <v>175</v>
+      </c>
+      <c r="F22" s="10">
+        <v>-18</v>
+      </c>
+      <c r="G22" s="10">
+        <v>-8.6300000000000008</v>
       </c>
       <c r="H22" s="9">
         <v>0</v>
@@ -2337,31 +2346,31 @@
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B23" s="7">
-        <v>243</v>
+        <v>188.5</v>
       </c>
       <c r="C23" s="7">
-        <v>188.5</v>
+        <v>208.5</v>
       </c>
       <c r="D23" s="7">
-        <v>254.5</v>
+        <v>211.5</v>
       </c>
       <c r="E23" s="7">
-        <v>174.5</v>
-      </c>
-      <c r="F23" s="10">
-        <v>-54.5</v>
-      </c>
-      <c r="G23" s="10">
-        <v>-22.43</v>
+        <v>140</v>
+      </c>
+      <c r="F23" s="8">
+        <v>20</v>
+      </c>
+      <c r="G23" s="8">
+        <v>10.61</v>
       </c>
       <c r="H23" s="9">
         <v>0</v>
       </c>
-      <c r="I23" s="10">
-        <v>-100</v>
+      <c r="I23" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>17</v>
@@ -2375,8 +2384,8 @@
       <c r="M23" s="9">
         <v>0</v>
       </c>
-      <c r="N23" s="10">
-        <v>-100</v>
+      <c r="N23" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>17</v>
@@ -2390,81 +2399,81 @@
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B24" s="7">
-        <v>236.5</v>
+        <v>243</v>
       </c>
       <c r="C24" s="7">
-        <v>243</v>
+        <v>188.5</v>
       </c>
       <c r="D24" s="7">
-        <v>269.5</v>
+        <v>254.5</v>
       </c>
       <c r="E24" s="7">
-        <v>228.5</v>
-      </c>
-      <c r="F24" s="8">
-        <v>6.5</v>
-      </c>
-      <c r="G24" s="8">
-        <v>2.75</v>
+        <v>174.5</v>
+      </c>
+      <c r="F24" s="10">
+        <v>-54.5</v>
+      </c>
+      <c r="G24" s="10">
+        <v>-22.43</v>
       </c>
       <c r="H24" s="9">
-        <v>8.3000000000000001E-3</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I24" s="10">
+        <v>-100</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K24" s="9">
-        <v>8.3000000000000001E-3</v>
-      </c>
-      <c r="L24" s="8">
-        <v>235.9</v>
+        <v>0</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M24" s="9">
-        <v>8.3000000000000001E-3</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N24" s="10">
+        <v>-100</v>
       </c>
       <c r="O24" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P24" s="9">
-        <v>8.3000000000000001E-3</v>
-      </c>
-      <c r="Q24" s="8">
-        <v>235.9</v>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B25" s="7">
-        <v>168</v>
+        <v>236.5</v>
       </c>
       <c r="C25" s="7">
-        <v>236.5</v>
+        <v>243</v>
       </c>
       <c r="D25" s="7">
-        <v>254.5</v>
+        <v>269.5</v>
       </c>
       <c r="E25" s="7">
-        <v>162.5</v>
+        <v>228.5</v>
       </c>
       <c r="F25" s="8">
-        <v>68.5</v>
+        <v>6.5</v>
       </c>
       <c r="G25" s="8">
-        <v>40.770000000000003</v>
+        <v>2.75</v>
       </c>
       <c r="H25" s="9">
-        <v>0</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="I25" s="9" t="s">
         <v>17</v>
@@ -2473,13 +2482,13 @@
         <v>17</v>
       </c>
       <c r="K25" s="9">
-        <v>0</v>
-      </c>
-      <c r="L25" s="10">
-        <v>-100</v>
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="L25" s="8">
+        <v>235.9</v>
       </c>
       <c r="M25" s="9">
-        <v>0</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="N25" s="9" t="s">
         <v>17</v>
@@ -2488,33 +2497,33 @@
         <v>17</v>
       </c>
       <c r="P25" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="10">
-        <v>-100</v>
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="Q25" s="8">
+        <v>235.9</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B26" s="7">
-        <v>149.5</v>
+        <v>168</v>
       </c>
       <c r="C26" s="7">
-        <v>168</v>
+        <v>236.5</v>
       </c>
       <c r="D26" s="7">
-        <v>177.5</v>
+        <v>254.5</v>
       </c>
       <c r="E26" s="7">
-        <v>140</v>
+        <v>162.5</v>
       </c>
       <c r="F26" s="8">
-        <v>18.5</v>
+        <v>68.5</v>
       </c>
       <c r="G26" s="8">
-        <v>12.37</v>
+        <v>40.770000000000003</v>
       </c>
       <c r="H26" s="9">
         <v>0</v>
@@ -2549,25 +2558,25 @@
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B27" s="7">
-        <v>147</v>
+        <v>149.5</v>
       </c>
       <c r="C27" s="7">
-        <v>149.5</v>
+        <v>168</v>
       </c>
       <c r="D27" s="7">
-        <v>174.5</v>
+        <v>177.5</v>
       </c>
       <c r="E27" s="7">
-        <v>140.5</v>
+        <v>140</v>
       </c>
       <c r="F27" s="8">
-        <v>2.5</v>
+        <v>18.5</v>
       </c>
       <c r="G27" s="8">
-        <v>1.7</v>
+        <v>12.37</v>
       </c>
       <c r="H27" s="9">
         <v>0</v>
@@ -2602,25 +2611,25 @@
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B28" s="7">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="C28" s="7">
-        <v>147</v>
+        <v>149.5</v>
       </c>
       <c r="D28" s="7">
-        <v>156</v>
+        <v>174.5</v>
       </c>
       <c r="E28" s="7">
-        <v>118.5</v>
+        <v>140.5</v>
       </c>
       <c r="F28" s="8">
-        <v>25</v>
+        <v>2.5</v>
       </c>
       <c r="G28" s="8">
-        <v>20.49</v>
+        <v>1.7</v>
       </c>
       <c r="H28" s="9">
         <v>0</v>
@@ -2655,25 +2664,25 @@
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B29" s="7">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="C29" s="7">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="D29" s="7">
-        <v>202</v>
+        <v>156</v>
       </c>
       <c r="E29" s="7">
-        <v>88.6</v>
+        <v>118.5</v>
       </c>
       <c r="F29" s="8">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G29" s="8">
-        <v>32.61</v>
+        <v>20.49</v>
       </c>
       <c r="H29" s="9">
         <v>0</v>
@@ -2708,25 +2717,25 @@
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B30" s="7">
-        <v>79.900000000000006</v>
+        <v>92</v>
       </c>
       <c r="C30" s="7">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="D30" s="7">
-        <v>92</v>
+        <v>202</v>
       </c>
       <c r="E30" s="7">
-        <v>75.400000000000006</v>
+        <v>88.6</v>
       </c>
       <c r="F30" s="8">
-        <v>12.1</v>
+        <v>30</v>
       </c>
       <c r="G30" s="8">
-        <v>15.14</v>
+        <v>32.61</v>
       </c>
       <c r="H30" s="9">
         <v>0</v>
@@ -2734,8 +2743,8 @@
       <c r="I30" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J30" s="10">
-        <v>-100</v>
+      <c r="J30" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K30" s="9">
         <v>0</v>
@@ -2749,8 +2758,8 @@
       <c r="N30" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O30" s="10">
-        <v>-100</v>
+      <c r="O30" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P30" s="9">
         <v>0</v>
@@ -2761,25 +2770,25 @@
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B31" s="7">
-        <v>62.9</v>
+        <v>79.900000000000006</v>
       </c>
       <c r="C31" s="7">
-        <v>79.900000000000006</v>
+        <v>92</v>
       </c>
       <c r="D31" s="7">
-        <v>83.5</v>
+        <v>92</v>
       </c>
       <c r="E31" s="7">
-        <v>61</v>
+        <v>75.400000000000006</v>
       </c>
       <c r="F31" s="8">
-        <v>17</v>
+        <v>12.1</v>
       </c>
       <c r="G31" s="8">
-        <v>27.03</v>
+        <v>15.14</v>
       </c>
       <c r="H31" s="9">
         <v>0</v>
@@ -2787,14 +2796,14 @@
       <c r="I31" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J31" s="9" t="s">
-        <v>17</v>
+      <c r="J31" s="10">
+        <v>-100</v>
       </c>
       <c r="K31" s="9">
         <v>0</v>
       </c>
-      <c r="L31" s="9" t="s">
-        <v>17</v>
+      <c r="L31" s="10">
+        <v>-100</v>
       </c>
       <c r="M31" s="9">
         <v>0</v>
@@ -2802,37 +2811,37 @@
       <c r="N31" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O31" s="9" t="s">
-        <v>17</v>
+      <c r="O31" s="10">
+        <v>-100</v>
       </c>
       <c r="P31" s="9">
         <v>0</v>
       </c>
-      <c r="Q31" s="9" t="s">
-        <v>17</v>
+      <c r="Q31" s="10">
+        <v>-100</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B32" s="7">
-        <v>63</v>
+        <v>62.9</v>
       </c>
       <c r="C32" s="7">
-        <v>62.9</v>
+        <v>79.900000000000006</v>
       </c>
       <c r="D32" s="7">
-        <v>62.9</v>
+        <v>83.5</v>
       </c>
       <c r="E32" s="7">
-        <v>58.1</v>
-      </c>
-      <c r="F32" s="10">
-        <v>-0.1</v>
-      </c>
-      <c r="G32" s="10">
-        <v>-0.16</v>
+        <v>61</v>
+      </c>
+      <c r="F32" s="8">
+        <v>17</v>
+      </c>
+      <c r="G32" s="8">
+        <v>27.03</v>
       </c>
       <c r="H32" s="9">
         <v>0</v>
@@ -2867,25 +2876,25 @@
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B33" s="7">
-        <v>74.989999999999995</v>
+        <v>63</v>
       </c>
       <c r="C33" s="7">
-        <v>63</v>
+        <v>62.9</v>
       </c>
       <c r="D33" s="7">
-        <v>75.77</v>
+        <v>62.9</v>
       </c>
       <c r="E33" s="7">
-        <v>53.71</v>
+        <v>58.1</v>
       </c>
       <c r="F33" s="10">
-        <v>-11.99</v>
+        <v>-0.1</v>
       </c>
       <c r="G33" s="10">
-        <v>-15.99</v>
+        <v>-0.16</v>
       </c>
       <c r="H33" s="9">
         <v>0</v>
@@ -2920,25 +2929,25 @@
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B34" s="7">
-        <v>74.290000000000006</v>
+        <v>74.989999999999995</v>
       </c>
       <c r="C34" s="7">
-        <v>74.989999999999995</v>
+        <v>63</v>
       </c>
       <c r="D34" s="7">
-        <v>74.989999999999995</v>
+        <v>75.77</v>
       </c>
       <c r="E34" s="7">
-        <v>67.45</v>
-      </c>
-      <c r="F34" s="8">
-        <v>0.7</v>
-      </c>
-      <c r="G34" s="8">
-        <v>0.94</v>
+        <v>53.71</v>
+      </c>
+      <c r="F34" s="10">
+        <v>-11.99</v>
+      </c>
+      <c r="G34" s="10">
+        <v>-15.99</v>
       </c>
       <c r="H34" s="9">
         <v>0</v>
@@ -2973,25 +2982,25 @@
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B35" s="7">
-        <v>79.989999999999995</v>
+        <v>74.290000000000006</v>
       </c>
       <c r="C35" s="7">
-        <v>74.290000000000006</v>
+        <v>74.989999999999995</v>
       </c>
       <c r="D35" s="7">
-        <v>87.99</v>
+        <v>74.989999999999995</v>
       </c>
       <c r="E35" s="7">
-        <v>66.510000000000005</v>
-      </c>
-      <c r="F35" s="10">
-        <v>-5.7</v>
-      </c>
-      <c r="G35" s="10">
-        <v>-7.13</v>
+        <v>67.45</v>
+      </c>
+      <c r="F35" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="G35" s="8">
+        <v>0.94</v>
       </c>
       <c r="H35" s="9">
         <v>0</v>
@@ -3026,25 +3035,25 @@
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B36" s="7">
-        <v>61.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="C36" s="7">
-        <v>79.989999999999995</v>
+        <v>74.290000000000006</v>
       </c>
       <c r="D36" s="7">
-        <v>80.989999999999995</v>
+        <v>87.99</v>
       </c>
       <c r="E36" s="7">
-        <v>58</v>
-      </c>
-      <c r="F36" s="8">
-        <v>18</v>
-      </c>
-      <c r="G36" s="8">
-        <v>29.04</v>
+        <v>66.510000000000005</v>
+      </c>
+      <c r="F36" s="10">
+        <v>-5.7</v>
+      </c>
+      <c r="G36" s="10">
+        <v>-7.13</v>
       </c>
       <c r="H36" s="9">
         <v>0</v>
@@ -3052,14 +3061,14 @@
       <c r="I36" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J36" s="10">
-        <v>-100</v>
+      <c r="J36" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K36" s="9">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="L36" s="8">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M36" s="9">
         <v>0</v>
@@ -3067,37 +3076,37 @@
       <c r="N36" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O36" s="10">
-        <v>-100</v>
+      <c r="O36" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P36" s="9">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="Q36" s="8">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B37" s="7">
-        <v>60.59</v>
+        <v>61.99</v>
       </c>
       <c r="C37" s="7">
-        <v>61.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="D37" s="7">
-        <v>62</v>
+        <v>80.989999999999995</v>
       </c>
       <c r="E37" s="7">
-        <v>57.71</v>
+        <v>58</v>
       </c>
       <c r="F37" s="8">
-        <v>1.4</v>
+        <v>18</v>
       </c>
       <c r="G37" s="8">
-        <v>2.31</v>
+        <v>29.04</v>
       </c>
       <c r="H37" s="9">
         <v>0</v>
@@ -3105,14 +3114,14 @@
       <c r="I37" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="9" t="s">
-        <v>17</v>
+      <c r="J37" s="10">
+        <v>-100</v>
       </c>
       <c r="K37" s="9">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="L37" s="9" t="s">
-        <v>17</v>
+      <c r="L37" s="8">
+        <v>300</v>
       </c>
       <c r="M37" s="9">
         <v>0</v>
@@ -3120,37 +3129,37 @@
       <c r="N37" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O37" s="9" t="s">
-        <v>17</v>
+      <c r="O37" s="10">
+        <v>-100</v>
       </c>
       <c r="P37" s="9">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="Q37" s="9" t="s">
-        <v>17</v>
+      <c r="Q37" s="8">
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B38" s="7">
-        <v>61</v>
+        <v>60.59</v>
       </c>
       <c r="C38" s="7">
-        <v>60.59</v>
+        <v>61.99</v>
       </c>
       <c r="D38" s="7">
-        <v>62.49</v>
+        <v>62</v>
       </c>
       <c r="E38" s="7">
-        <v>57.76</v>
-      </c>
-      <c r="F38" s="10">
-        <v>-0.41</v>
-      </c>
-      <c r="G38" s="10">
-        <v>-0.67</v>
+        <v>57.71</v>
+      </c>
+      <c r="F38" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="G38" s="8">
+        <v>2.31</v>
       </c>
       <c r="H38" s="9">
         <v>0</v>
@@ -3185,25 +3194,25 @@
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B39" s="7">
-        <v>58.89</v>
+        <v>61</v>
       </c>
       <c r="C39" s="7">
-        <v>61</v>
+        <v>60.59</v>
       </c>
       <c r="D39" s="7">
-        <v>62.99</v>
+        <v>62.49</v>
       </c>
       <c r="E39" s="7">
-        <v>57.01</v>
-      </c>
-      <c r="F39" s="8">
-        <v>2.11</v>
-      </c>
-      <c r="G39" s="8">
-        <v>3.58</v>
+        <v>57.76</v>
+      </c>
+      <c r="F39" s="10">
+        <v>-0.41</v>
+      </c>
+      <c r="G39" s="10">
+        <v>-0.67</v>
       </c>
       <c r="H39" s="9">
         <v>0</v>
@@ -3238,25 +3247,25 @@
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B40" s="7">
-        <v>60.5</v>
+        <v>58.89</v>
       </c>
       <c r="C40" s="7">
-        <v>58.89</v>
+        <v>61</v>
       </c>
       <c r="D40" s="7">
-        <v>62.09</v>
+        <v>62.99</v>
       </c>
       <c r="E40" s="7">
-        <v>56.7</v>
-      </c>
-      <c r="F40" s="10">
-        <v>-1.61</v>
-      </c>
-      <c r="G40" s="10">
-        <v>-2.66</v>
+        <v>57.01</v>
+      </c>
+      <c r="F40" s="8">
+        <v>2.11</v>
+      </c>
+      <c r="G40" s="8">
+        <v>3.58</v>
       </c>
       <c r="H40" s="9">
         <v>0</v>
@@ -3291,31 +3300,31 @@
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B41" s="7">
-        <v>58.3</v>
+        <v>60.5</v>
       </c>
       <c r="C41" s="7">
-        <v>60.5</v>
+        <v>58.89</v>
       </c>
       <c r="D41" s="7">
-        <v>63.6</v>
+        <v>62.09</v>
       </c>
       <c r="E41" s="7">
-        <v>57.5</v>
-      </c>
-      <c r="F41" s="8">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="G41" s="8">
-        <v>3.77</v>
+        <v>56.7</v>
+      </c>
+      <c r="F41" s="10">
+        <v>-1.61</v>
+      </c>
+      <c r="G41" s="10">
+        <v>-2.66</v>
       </c>
       <c r="H41" s="9">
         <v>0</v>
       </c>
-      <c r="I41" s="10">
-        <v>-100</v>
+      <c r="I41" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>17</v>
@@ -3329,8 +3338,8 @@
       <c r="M41" s="9">
         <v>0</v>
       </c>
-      <c r="N41" s="10">
-        <v>-100</v>
+      <c r="N41" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>17</v>
@@ -3344,31 +3353,31 @@
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B42" s="7">
         <v>58.3</v>
       </c>
       <c r="C42" s="7">
-        <v>58.3</v>
+        <v>60.5</v>
       </c>
       <c r="D42" s="7">
-        <v>58.9</v>
+        <v>63.6</v>
       </c>
       <c r="E42" s="7">
-        <v>52.7</v>
-      </c>
-      <c r="F42" s="9">
-        <v>0</v>
-      </c>
-      <c r="G42" s="9">
-        <v>0</v>
+        <v>57.5</v>
+      </c>
+      <c r="F42" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G42" s="8">
+        <v>3.77</v>
       </c>
       <c r="H42" s="9">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I42" s="10">
+        <v>-100</v>
       </c>
       <c r="J42" s="9" t="s">
         <v>17</v>
@@ -3380,10 +3389,10 @@
         <v>17</v>
       </c>
       <c r="M42" s="9">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="N42" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N42" s="10">
+        <v>-100</v>
       </c>
       <c r="O42" s="9" t="s">
         <v>17</v>
@@ -3397,28 +3406,28 @@
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B43" s="7">
-        <v>64</v>
+        <v>58.3</v>
       </c>
       <c r="C43" s="7">
         <v>58.3</v>
       </c>
       <c r="D43" s="7">
-        <v>64</v>
+        <v>58.9</v>
       </c>
       <c r="E43" s="7">
-        <v>56</v>
-      </c>
-      <c r="F43" s="10">
-        <v>-5.7</v>
-      </c>
-      <c r="G43" s="10">
-        <v>-8.91</v>
+        <v>52.7</v>
+      </c>
+      <c r="F43" s="9">
+        <v>0</v>
+      </c>
+      <c r="G43" s="9">
+        <v>0</v>
       </c>
       <c r="H43" s="9">
-        <v>0</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="I43" s="9" t="s">
         <v>17</v>
@@ -3427,13 +3436,13 @@
         <v>17</v>
       </c>
       <c r="K43" s="9">
-        <v>0</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="L43" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M43" s="9">
-        <v>0</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="N43" s="9" t="s">
         <v>17</v>
@@ -3442,7 +3451,7 @@
         <v>17</v>
       </c>
       <c r="P43" s="9">
-        <v>0</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="Q43" s="9" t="s">
         <v>17</v>
@@ -3450,25 +3459,25 @@
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B44" s="7">
-        <v>65.5</v>
+        <v>64</v>
       </c>
       <c r="C44" s="7">
+        <v>58.3</v>
+      </c>
+      <c r="D44" s="7">
         <v>64</v>
       </c>
-      <c r="D44" s="7">
-        <v>65.5</v>
-      </c>
       <c r="E44" s="7">
-        <v>60.15</v>
+        <v>56</v>
       </c>
       <c r="F44" s="10">
-        <v>-1.5</v>
+        <v>-5.7</v>
       </c>
       <c r="G44" s="10">
-        <v>-2.29</v>
+        <v>-8.91</v>
       </c>
       <c r="H44" s="9">
         <v>0</v>
@@ -3503,25 +3512,25 @@
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B45" s="7">
-        <v>65.3</v>
+        <v>65.5</v>
       </c>
       <c r="C45" s="7">
+        <v>64</v>
+      </c>
+      <c r="D45" s="7">
         <v>65.5</v>
       </c>
-      <c r="D45" s="7">
-        <v>66.7</v>
-      </c>
       <c r="E45" s="7">
-        <v>64</v>
-      </c>
-      <c r="F45" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="G45" s="8">
-        <v>0.31</v>
+        <v>60.15</v>
+      </c>
+      <c r="F45" s="10">
+        <v>-1.5</v>
+      </c>
+      <c r="G45" s="10">
+        <v>-2.29</v>
       </c>
       <c r="H45" s="9">
         <v>0</v>
@@ -3556,25 +3565,25 @@
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B46" s="7">
-        <v>65.69</v>
+        <v>65.3</v>
       </c>
       <c r="C46" s="7">
-        <v>65.3</v>
+        <v>65.5</v>
       </c>
       <c r="D46" s="7">
-        <v>66.31</v>
+        <v>66.7</v>
       </c>
       <c r="E46" s="7">
-        <v>61.28</v>
-      </c>
-      <c r="F46" s="10">
-        <v>-0.39</v>
-      </c>
-      <c r="G46" s="10">
-        <v>-0.59</v>
+        <v>64</v>
+      </c>
+      <c r="F46" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="G46" s="8">
+        <v>0.31</v>
       </c>
       <c r="H46" s="9">
         <v>0</v>
@@ -3609,31 +3618,31 @@
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B47" s="7">
-        <v>66.8</v>
+        <v>65.69</v>
       </c>
       <c r="C47" s="7">
-        <v>65.69</v>
+        <v>65.3</v>
       </c>
       <c r="D47" s="7">
-        <v>67.48</v>
+        <v>66.31</v>
       </c>
       <c r="E47" s="7">
-        <v>62.52</v>
+        <v>61.28</v>
       </c>
       <c r="F47" s="10">
-        <v>-1.1100000000000001</v>
+        <v>-0.39</v>
       </c>
       <c r="G47" s="10">
-        <v>-1.66</v>
+        <v>-0.59</v>
       </c>
       <c r="H47" s="9">
         <v>0</v>
       </c>
-      <c r="I47" s="10">
-        <v>-100</v>
+      <c r="I47" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J47" s="9" t="s">
         <v>17</v>
@@ -3647,8 +3656,8 @@
       <c r="M47" s="9">
         <v>0</v>
       </c>
-      <c r="N47" s="10">
-        <v>-100</v>
+      <c r="N47" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>17</v>
@@ -3662,131 +3671,131 @@
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B48" s="7">
-        <v>69.78</v>
+        <v>66.8</v>
       </c>
       <c r="C48" s="7">
-        <v>66.8</v>
+        <v>65.69</v>
       </c>
       <c r="D48" s="7">
-        <v>69.78</v>
+        <v>67.48</v>
       </c>
       <c r="E48" s="7">
-        <v>64.05</v>
+        <v>62.52</v>
       </c>
       <c r="F48" s="10">
-        <v>-2.98</v>
+        <v>-1.1100000000000001</v>
       </c>
       <c r="G48" s="10">
-        <v>-4.2699999999999996</v>
+        <v>-1.66</v>
       </c>
       <c r="H48" s="9">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="I48" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="10">
-        <v>-27.9</v>
+        <v>0</v>
+      </c>
+      <c r="I48" s="10">
+        <v>-100</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K48" s="9">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="L48" s="10">
-        <v>-94.1</v>
+        <v>0</v>
+      </c>
+      <c r="L48" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M48" s="9">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="N48" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O48" s="10">
-        <v>-27.9</v>
+        <v>0</v>
+      </c>
+      <c r="N48" s="10">
+        <v>-100</v>
+      </c>
+      <c r="O48" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P48" s="9">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="Q48" s="10">
-        <v>-94.1</v>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B49" s="7">
-        <v>65.98</v>
+        <v>69.78</v>
       </c>
       <c r="C49" s="7">
+        <v>66.8</v>
+      </c>
+      <c r="D49" s="7">
         <v>69.78</v>
       </c>
-      <c r="D49" s="7">
-        <v>72</v>
-      </c>
       <c r="E49" s="7">
-        <v>65.05</v>
-      </c>
-      <c r="F49" s="8">
-        <v>3.8</v>
-      </c>
-      <c r="G49" s="8">
-        <v>5.76</v>
+        <v>64.05</v>
+      </c>
+      <c r="F49" s="10">
+        <v>-2.98</v>
+      </c>
+      <c r="G49" s="10">
+        <v>-4.2699999999999996</v>
       </c>
       <c r="H49" s="9">
-        <v>0</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="I49" s="9" t="s">
         <v>17</v>
       </c>
       <c r="J49" s="10">
-        <v>-100</v>
+        <v>-27.9</v>
       </c>
       <c r="K49" s="9">
-        <v>0</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="L49" s="10">
-        <v>-100</v>
+        <v>-94.1</v>
       </c>
       <c r="M49" s="9">
-        <v>0</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="N49" s="9" t="s">
         <v>17</v>
       </c>
       <c r="O49" s="10">
-        <v>-100</v>
+        <v>-27.9</v>
       </c>
       <c r="P49" s="9">
-        <v>0</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="Q49" s="10">
-        <v>-100</v>
+        <v>-94.1</v>
       </c>
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B50" s="7">
-        <v>67.5</v>
+        <v>65.98</v>
       </c>
       <c r="C50" s="7">
-        <v>65.98</v>
+        <v>69.78</v>
       </c>
       <c r="D50" s="7">
-        <v>82.1</v>
+        <v>72</v>
       </c>
       <c r="E50" s="7">
-        <v>62</v>
-      </c>
-      <c r="F50" s="10">
-        <v>-1.52</v>
-      </c>
-      <c r="G50" s="10">
-        <v>-2.25</v>
+        <v>65.05</v>
+      </c>
+      <c r="F50" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G50" s="8">
+        <v>5.76</v>
       </c>
       <c r="H50" s="9">
         <v>0</v>
@@ -3821,25 +3830,25 @@
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B51" s="7">
-        <v>66.599999999999994</v>
+        <v>67.5</v>
       </c>
       <c r="C51" s="7">
-        <v>67.5</v>
+        <v>65.98</v>
       </c>
       <c r="D51" s="7">
-        <v>70</v>
+        <v>82.1</v>
       </c>
       <c r="E51" s="7">
-        <v>63.72</v>
-      </c>
-      <c r="F51" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="G51" s="8">
-        <v>1.35</v>
+        <v>62</v>
+      </c>
+      <c r="F51" s="10">
+        <v>-1.52</v>
+      </c>
+      <c r="G51" s="10">
+        <v>-2.25</v>
       </c>
       <c r="H51" s="9">
         <v>0</v>
@@ -3874,25 +3883,25 @@
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B52" s="7">
-        <v>65.98</v>
+        <v>66.599999999999994</v>
       </c>
       <c r="C52" s="7">
-        <v>66.599999999999994</v>
+        <v>67.5</v>
       </c>
       <c r="D52" s="7">
-        <v>67.5</v>
+        <v>70</v>
       </c>
       <c r="E52" s="7">
-        <v>62.72</v>
+        <v>63.72</v>
       </c>
       <c r="F52" s="8">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
       <c r="G52" s="8">
-        <v>0.94</v>
+        <v>1.35</v>
       </c>
       <c r="H52" s="9">
         <v>0</v>
@@ -3927,25 +3936,25 @@
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B53" s="7">
-        <v>65.45</v>
+        <v>65.98</v>
       </c>
       <c r="C53" s="7">
-        <v>65.98</v>
+        <v>66.599999999999994</v>
       </c>
       <c r="D53" s="7">
-        <v>68</v>
+        <v>67.5</v>
       </c>
       <c r="E53" s="7">
-        <v>61.77</v>
+        <v>62.72</v>
       </c>
       <c r="F53" s="8">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="G53" s="8">
-        <v>0.81</v>
+        <v>0.94</v>
       </c>
       <c r="H53" s="9">
         <v>0</v>
@@ -3980,25 +3989,25 @@
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B54" s="7">
-        <v>62.45</v>
+        <v>65.45</v>
       </c>
       <c r="C54" s="7">
-        <v>65.45</v>
+        <v>65.98</v>
       </c>
       <c r="D54" s="7">
-        <v>66.5</v>
+        <v>68</v>
       </c>
       <c r="E54" s="7">
-        <v>56.53</v>
+        <v>61.77</v>
       </c>
       <c r="F54" s="8">
-        <v>3</v>
+        <v>0.53</v>
       </c>
       <c r="G54" s="8">
-        <v>4.8</v>
+        <v>0.81</v>
       </c>
       <c r="H54" s="9">
         <v>0</v>
@@ -4033,31 +4042,31 @@
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B55" s="7">
-        <v>69.099999999999994</v>
+        <v>62.45</v>
       </c>
       <c r="C55" s="7">
-        <v>62.45</v>
+        <v>65.45</v>
       </c>
       <c r="D55" s="7">
-        <v>70.34</v>
+        <v>66.5</v>
       </c>
       <c r="E55" s="7">
-        <v>60</v>
-      </c>
-      <c r="F55" s="10">
-        <v>-6.65</v>
-      </c>
-      <c r="G55" s="10">
-        <v>-9.6199999999999992</v>
+        <v>56.53</v>
+      </c>
+      <c r="F55" s="8">
+        <v>3</v>
+      </c>
+      <c r="G55" s="8">
+        <v>4.8</v>
       </c>
       <c r="H55" s="9">
         <v>0</v>
       </c>
-      <c r="I55" s="10">
-        <v>-100</v>
+      <c r="I55" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J55" s="10">
         <v>-100</v>
@@ -4071,8 +4080,8 @@
       <c r="M55" s="9">
         <v>0</v>
       </c>
-      <c r="N55" s="10">
-        <v>-100</v>
+      <c r="N55" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O55" s="10">
         <v>-100</v>
@@ -4086,25 +4095,25 @@
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B56" s="7">
-        <v>68.5</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="C56" s="7">
-        <v>69.099999999999994</v>
+        <v>62.45</v>
       </c>
       <c r="D56" s="7">
-        <v>71.05</v>
+        <v>70.34</v>
       </c>
       <c r="E56" s="7">
-        <v>64.06</v>
-      </c>
-      <c r="F56" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="G56" s="8">
-        <v>0.88</v>
+        <v>60</v>
+      </c>
+      <c r="F56" s="10">
+        <v>-6.65</v>
+      </c>
+      <c r="G56" s="10">
+        <v>-9.6199999999999992</v>
       </c>
       <c r="H56" s="9">
         <v>0</v>
@@ -4139,25 +4148,25 @@
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B57" s="7">
-        <v>66.98</v>
+        <v>68.5</v>
       </c>
       <c r="C57" s="7">
-        <v>68.5</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="D57" s="7">
-        <v>74.73</v>
+        <v>71.05</v>
       </c>
       <c r="E57" s="7">
-        <v>59</v>
+        <v>64.06</v>
       </c>
       <c r="F57" s="8">
-        <v>1.52</v>
+        <v>0.6</v>
       </c>
       <c r="G57" s="8">
-        <v>2.27</v>
+        <v>0.88</v>
       </c>
       <c r="H57" s="9">
         <v>0</v>
@@ -4192,25 +4201,25 @@
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B58" s="7">
-        <v>72.8</v>
+        <v>66.98</v>
       </c>
       <c r="C58" s="7">
-        <v>66.98</v>
+        <v>68.5</v>
       </c>
       <c r="D58" s="7">
-        <v>73</v>
+        <v>74.73</v>
       </c>
       <c r="E58" s="7">
-        <v>64</v>
-      </c>
-      <c r="F58" s="10">
-        <v>-5.82</v>
-      </c>
-      <c r="G58" s="10">
-        <v>-7.99</v>
+        <v>59</v>
+      </c>
+      <c r="F58" s="8">
+        <v>1.52</v>
+      </c>
+      <c r="G58" s="8">
+        <v>2.27</v>
       </c>
       <c r="H58" s="9">
         <v>0</v>
@@ -4245,25 +4254,25 @@
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B59" s="7">
-        <v>65</v>
+        <v>72.8</v>
       </c>
       <c r="C59" s="7">
-        <v>72.8</v>
+        <v>66.98</v>
       </c>
       <c r="D59" s="7">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E59" s="7">
-        <v>65.5</v>
-      </c>
-      <c r="F59" s="8">
-        <v>7.8</v>
-      </c>
-      <c r="G59" s="8">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="F59" s="10">
+        <v>-5.82</v>
+      </c>
+      <c r="G59" s="10">
+        <v>-7.99</v>
       </c>
       <c r="H59" s="9">
         <v>0</v>
@@ -4298,143 +4307,143 @@
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B60" s="7">
-        <v>55.77</v>
+        <v>65</v>
       </c>
       <c r="C60" s="7">
-        <v>65</v>
+        <v>72.8</v>
       </c>
       <c r="D60" s="7">
-        <v>65.98</v>
+        <v>80</v>
       </c>
       <c r="E60" s="7">
-        <v>53.3</v>
+        <v>65.5</v>
       </c>
       <c r="F60" s="8">
-        <v>9.23</v>
+        <v>7.8</v>
       </c>
       <c r="G60" s="8">
-        <v>16.55</v>
+        <v>12</v>
       </c>
       <c r="H60" s="9">
-        <v>8.9999999999999998E-4</v>
+        <v>0</v>
       </c>
       <c r="I60" s="10">
-        <v>-1.1399999999999999</v>
+        <v>-100</v>
       </c>
       <c r="J60" s="10">
-        <v>-7.52</v>
+        <v>-100</v>
       </c>
       <c r="K60" s="9">
-        <v>1.0500000000000001E-2</v>
-      </c>
-      <c r="L60" s="8">
-        <v>1028</v>
+        <v>0</v>
+      </c>
+      <c r="L60" s="10">
+        <v>-100</v>
       </c>
       <c r="M60" s="9">
-        <v>8.9999999999999998E-4</v>
+        <v>0</v>
       </c>
       <c r="N60" s="10">
-        <v>-1.1399999999999999</v>
+        <v>-100</v>
       </c>
       <c r="O60" s="10">
-        <v>-7.52</v>
+        <v>-100</v>
       </c>
       <c r="P60" s="9">
-        <v>1.0500000000000001E-2</v>
-      </c>
-      <c r="Q60" s="8">
-        <v>1028</v>
+        <v>0</v>
+      </c>
+      <c r="Q60" s="10">
+        <v>-100</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B61" s="7">
-        <v>55.18</v>
+        <v>55.77</v>
       </c>
       <c r="C61" s="7">
-        <v>55.77</v>
+        <v>65</v>
       </c>
       <c r="D61" s="7">
-        <v>56</v>
+        <v>65.98</v>
       </c>
       <c r="E61" s="7">
-        <v>52.5</v>
+        <v>53.3</v>
       </c>
       <c r="F61" s="8">
-        <v>0.59</v>
+        <v>9.23</v>
       </c>
       <c r="G61" s="8">
-        <v>1.07</v>
+        <v>16.55</v>
       </c>
       <c r="H61" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I61" s="9">
-        <v>0</v>
-      </c>
-      <c r="J61" s="9" t="s">
-        <v>17</v>
+      <c r="I61" s="10">
+        <v>-1.1399999999999999</v>
+      </c>
+      <c r="J61" s="10">
+        <v>-7.52</v>
       </c>
       <c r="K61" s="9">
-        <v>9.5999999999999992E-3</v>
-      </c>
-      <c r="L61" s="9" t="s">
-        <v>17</v>
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="L61" s="8">
+        <v>1028</v>
       </c>
       <c r="M61" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N61" s="9">
-        <v>0</v>
-      </c>
-      <c r="O61" s="9" t="s">
-        <v>17</v>
+      <c r="N61" s="10">
+        <v>-1.1399999999999999</v>
+      </c>
+      <c r="O61" s="10">
+        <v>-7.52</v>
       </c>
       <c r="P61" s="9">
-        <v>9.5999999999999992E-3</v>
-      </c>
-      <c r="Q61" s="9" t="s">
-        <v>17</v>
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="Q61" s="8">
+        <v>1028</v>
       </c>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B62" s="7">
-        <v>54</v>
+        <v>55.18</v>
       </c>
       <c r="C62" s="7">
-        <v>55.18</v>
+        <v>55.77</v>
       </c>
       <c r="D62" s="7">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E62" s="7">
-        <v>52</v>
+        <v>52.5</v>
       </c>
       <c r="F62" s="8">
-        <v>1.18</v>
+        <v>0.59</v>
       </c>
       <c r="G62" s="8">
-        <v>2.19</v>
+        <v>1.07</v>
       </c>
       <c r="H62" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I62" s="10">
-        <v>-1.1299999999999999</v>
+      <c r="I62" s="9">
+        <v>0</v>
       </c>
       <c r="J62" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K62" s="9">
-        <v>8.8000000000000005E-3</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="L62" s="9" t="s">
         <v>17</v>
@@ -4442,14 +4451,14 @@
       <c r="M62" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N62" s="10">
-        <v>-1.1299999999999999</v>
+      <c r="N62" s="9">
+        <v>0</v>
       </c>
       <c r="O62" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P62" s="9">
-        <v>8.8000000000000005E-3</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="Q62" s="9" t="s">
         <v>17</v>
@@ -4457,37 +4466,37 @@
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>42979</v>
+        <v>43009</v>
       </c>
       <c r="B63" s="7">
-        <v>53.8</v>
+        <v>54</v>
       </c>
       <c r="C63" s="7">
-        <v>54</v>
+        <v>55.18</v>
       </c>
       <c r="D63" s="7">
-        <v>59.2</v>
+        <v>58</v>
       </c>
       <c r="E63" s="7">
-        <v>50.35</v>
+        <v>52</v>
       </c>
       <c r="F63" s="8">
-        <v>0.2</v>
+        <v>1.18</v>
       </c>
       <c r="G63" s="8">
-        <v>0.37</v>
+        <v>2.19</v>
       </c>
       <c r="H63" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I63" s="8">
-        <v>1.1399999999999999</v>
+      <c r="I63" s="10">
+        <v>-1.1299999999999999</v>
       </c>
       <c r="J63" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K63" s="9">
-        <v>7.9000000000000008E-3</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="L63" s="9" t="s">
         <v>17</v>
@@ -4495,14 +4504,14 @@
       <c r="M63" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N63" s="8">
-        <v>1.1399999999999999</v>
+      <c r="N63" s="10">
+        <v>-1.1299999999999999</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P63" s="9">
-        <v>7.9000000000000008E-3</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="Q63" s="9" t="s">
         <v>17</v>
@@ -4510,37 +4519,37 @@
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B64" s="7">
-        <v>56.88</v>
+        <v>53.8</v>
       </c>
       <c r="C64" s="7">
-        <v>53.8</v>
+        <v>54</v>
       </c>
       <c r="D64" s="7">
-        <v>56.98</v>
+        <v>59.2</v>
       </c>
       <c r="E64" s="7">
-        <v>52</v>
-      </c>
-      <c r="F64" s="10">
-        <v>-3.08</v>
-      </c>
-      <c r="G64" s="10">
-        <v>-5.41</v>
+        <v>50.35</v>
+      </c>
+      <c r="F64" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="G64" s="8">
+        <v>0.37</v>
       </c>
       <c r="H64" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I64" s="9">
-        <v>0</v>
+      <c r="I64" s="8">
+        <v>1.1399999999999999</v>
       </c>
       <c r="J64" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K64" s="9">
-        <v>7.0000000000000001E-3</v>
+        <v>7.9000000000000008E-3</v>
       </c>
       <c r="L64" s="9" t="s">
         <v>17</v>
@@ -4548,14 +4557,14 @@
       <c r="M64" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N64" s="9">
-        <v>0</v>
+      <c r="N64" s="8">
+        <v>1.1399999999999999</v>
       </c>
       <c r="O64" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P64" s="9">
-        <v>7.0000000000000001E-3</v>
+        <v>7.9000000000000008E-3</v>
       </c>
       <c r="Q64" s="9" t="s">
         <v>17</v>
@@ -4563,37 +4572,37 @@
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>42917</v>
+        <v>42948</v>
       </c>
       <c r="B65" s="7">
-        <v>63.45</v>
+        <v>56.88</v>
       </c>
       <c r="C65" s="7">
-        <v>56.88</v>
+        <v>53.8</v>
       </c>
       <c r="D65" s="7">
-        <v>63.5</v>
+        <v>56.98</v>
       </c>
       <c r="E65" s="7">
-        <v>47.5</v>
+        <v>52</v>
       </c>
       <c r="F65" s="10">
-        <v>-6.57</v>
+        <v>-3.08</v>
       </c>
       <c r="G65" s="10">
-        <v>-10.35</v>
+        <v>-5.41</v>
       </c>
       <c r="H65" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I65" s="10">
-        <v>-1.1299999999999999</v>
+      <c r="I65" s="9">
+        <v>0</v>
       </c>
       <c r="J65" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K65" s="9">
-        <v>6.1999999999999998E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="L65" s="9" t="s">
         <v>17</v>
@@ -4601,14 +4610,14 @@
       <c r="M65" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N65" s="10">
-        <v>-1.1299999999999999</v>
+      <c r="N65" s="9">
+        <v>0</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P65" s="9">
-        <v>6.1999999999999998E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="Q65" s="9" t="s">
         <v>17</v>
@@ -4616,37 +4625,37 @@
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>42887</v>
+        <v>42917</v>
       </c>
       <c r="B66" s="7">
-        <v>60.5</v>
+        <v>63.45</v>
       </c>
       <c r="C66" s="7">
-        <v>63.45</v>
+        <v>56.88</v>
       </c>
       <c r="D66" s="7">
-        <v>69.5</v>
+        <v>63.5</v>
       </c>
       <c r="E66" s="7">
-        <v>60</v>
-      </c>
-      <c r="F66" s="8">
-        <v>2.95</v>
-      </c>
-      <c r="G66" s="8">
-        <v>4.88</v>
+        <v>47.5</v>
+      </c>
+      <c r="F66" s="10">
+        <v>-6.57</v>
+      </c>
+      <c r="G66" s="10">
+        <v>-10.35</v>
       </c>
       <c r="H66" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I66" s="8">
-        <v>1.1399999999999999</v>
+      <c r="I66" s="10">
+        <v>-1.1299999999999999</v>
       </c>
       <c r="J66" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K66" s="9">
-        <v>5.3E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="L66" s="9" t="s">
         <v>17</v>
@@ -4654,14 +4663,14 @@
       <c r="M66" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N66" s="8">
-        <v>1.1399999999999999</v>
+      <c r="N66" s="10">
+        <v>-1.1299999999999999</v>
       </c>
       <c r="O66" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P66" s="9">
-        <v>5.3E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="Q66" s="9" t="s">
         <v>17</v>
@@ -4669,37 +4678,37 @@
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>42856</v>
+        <v>42887</v>
       </c>
       <c r="B67" s="7">
-        <v>67.5</v>
+        <v>60.5</v>
       </c>
       <c r="C67" s="7">
-        <v>60.5</v>
+        <v>63.45</v>
       </c>
       <c r="D67" s="7">
-        <v>67.48</v>
+        <v>69.5</v>
       </c>
       <c r="E67" s="7">
-        <v>57</v>
-      </c>
-      <c r="F67" s="10">
-        <v>-7</v>
-      </c>
-      <c r="G67" s="10">
-        <v>-10.37</v>
+        <v>60</v>
+      </c>
+      <c r="F67" s="8">
+        <v>2.95</v>
+      </c>
+      <c r="G67" s="8">
+        <v>4.88</v>
       </c>
       <c r="H67" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I67" s="9">
-        <v>0</v>
+      <c r="I67" s="8">
+        <v>1.1399999999999999</v>
       </c>
       <c r="J67" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K67" s="9">
-        <v>4.4000000000000003E-3</v>
+        <v>5.3E-3</v>
       </c>
       <c r="L67" s="9" t="s">
         <v>17</v>
@@ -4707,14 +4716,14 @@
       <c r="M67" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N67" s="9">
-        <v>0</v>
+      <c r="N67" s="8">
+        <v>1.1399999999999999</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P67" s="9">
-        <v>4.4000000000000003E-3</v>
+        <v>5.3E-3</v>
       </c>
       <c r="Q67" s="9" t="s">
         <v>17</v>
@@ -4722,37 +4731,37 @@
     </row>
     <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>42826</v>
+        <v>42856</v>
       </c>
       <c r="B68" s="7">
-        <v>72.099999999999994</v>
+        <v>67.5</v>
       </c>
       <c r="C68" s="7">
-        <v>67.5</v>
+        <v>60.5</v>
       </c>
       <c r="D68" s="7">
-        <v>75.78</v>
+        <v>67.48</v>
       </c>
       <c r="E68" s="7">
-        <v>61.51</v>
+        <v>57</v>
       </c>
       <c r="F68" s="10">
-        <v>-4.5999999999999996</v>
+        <v>-7</v>
       </c>
       <c r="G68" s="10">
-        <v>-6.38</v>
+        <v>-10.37</v>
       </c>
       <c r="H68" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I68" s="10">
-        <v>-1.1299999999999999</v>
+      <c r="I68" s="9">
+        <v>0</v>
       </c>
       <c r="J68" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K68" s="9">
-        <v>3.5000000000000001E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="L68" s="9" t="s">
         <v>17</v>
@@ -4760,14 +4769,14 @@
       <c r="M68" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N68" s="10">
-        <v>-1.1299999999999999</v>
+      <c r="N68" s="9">
+        <v>0</v>
       </c>
       <c r="O68" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P68" s="9">
-        <v>3.5000000000000001E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="Q68" s="9" t="s">
         <v>17</v>
@@ -4775,37 +4784,37 @@
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>42795</v>
+        <v>42826</v>
       </c>
       <c r="B69" s="7">
-        <v>84.29</v>
+        <v>72.099999999999994</v>
       </c>
       <c r="C69" s="7">
-        <v>72.099999999999994</v>
+        <v>67.5</v>
       </c>
       <c r="D69" s="7">
-        <v>84.5</v>
+        <v>75.78</v>
       </c>
       <c r="E69" s="7">
-        <v>68.02</v>
+        <v>61.51</v>
       </c>
       <c r="F69" s="10">
-        <v>-12.19</v>
+        <v>-4.5999999999999996</v>
       </c>
       <c r="G69" s="10">
-        <v>-14.46</v>
+        <v>-6.38</v>
       </c>
       <c r="H69" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I69" s="9">
-        <v>0</v>
+      <c r="I69" s="10">
+        <v>-1.1299999999999999</v>
       </c>
       <c r="J69" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K69" s="9">
-        <v>2.7000000000000001E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="L69" s="9" t="s">
         <v>17</v>
@@ -4813,14 +4822,14 @@
       <c r="M69" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N69" s="9">
-        <v>0</v>
+      <c r="N69" s="10">
+        <v>-1.1299999999999999</v>
       </c>
       <c r="O69" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P69" s="9">
-        <v>2.7000000000000001E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="Q69" s="9" t="s">
         <v>17</v>
@@ -4828,37 +4837,37 @@
     </row>
     <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>42767</v>
+        <v>42795</v>
       </c>
       <c r="B70" s="7">
-        <v>91.2</v>
+        <v>84.29</v>
       </c>
       <c r="C70" s="7">
-        <v>84.29</v>
+        <v>72.099999999999994</v>
       </c>
       <c r="D70" s="7">
-        <v>100</v>
+        <v>84.5</v>
       </c>
       <c r="E70" s="7">
-        <v>81.7</v>
+        <v>68.02</v>
       </c>
       <c r="F70" s="10">
-        <v>-7.91</v>
+        <v>-12.19</v>
       </c>
       <c r="G70" s="10">
-        <v>-8.58</v>
+        <v>-14.46</v>
       </c>
       <c r="H70" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I70" s="10">
-        <v>-2.2200000000000002</v>
+      <c r="I70" s="9">
+        <v>0</v>
       </c>
       <c r="J70" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K70" s="9">
-        <v>1.8E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="L70" s="9" t="s">
         <v>17</v>
@@ -4866,14 +4875,14 @@
       <c r="M70" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N70" s="10">
-        <v>-2.2200000000000002</v>
+      <c r="N70" s="9">
+        <v>0</v>
       </c>
       <c r="O70" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P70" s="9">
-        <v>1.8E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="Q70" s="9" t="s">
         <v>17</v>
@@ -4881,37 +4890,37 @@
     </row>
     <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>42736</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E71" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>17</v>
+        <v>42767</v>
+      </c>
+      <c r="B71" s="7">
+        <v>91.2</v>
+      </c>
+      <c r="C71" s="7">
+        <v>84.29</v>
+      </c>
+      <c r="D71" s="7">
+        <v>100</v>
+      </c>
+      <c r="E71" s="7">
+        <v>81.7</v>
+      </c>
+      <c r="F71" s="10">
+        <v>-7.91</v>
+      </c>
+      <c r="G71" s="10">
+        <v>-8.58</v>
       </c>
       <c r="H71" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="I71" s="9" t="s">
-        <v>17</v>
+      <c r="I71" s="10">
+        <v>-2.2200000000000002</v>
       </c>
       <c r="J71" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K71" s="9">
-        <v>8.9999999999999998E-4</v>
+        <v>1.8E-3</v>
       </c>
       <c r="L71" s="9" t="s">
         <v>17</v>
@@ -4919,16 +4928,69 @@
       <c r="M71" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="N71" s="9" t="s">
-        <v>17</v>
+      <c r="N71" s="10">
+        <v>-2.2200000000000002</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P71" s="9">
+        <v>1.8E-3</v>
+      </c>
+      <c r="Q71" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>42736</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H72" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="Q71" s="9" t="s">
+      <c r="I72" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K72" s="9">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="L72" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M72" s="9">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="N72" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O72" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P72" s="9">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="Q72" s="9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4947,7 +5009,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>